--- a/outputs/candidates/baseline/candidate_04_fatigue.xlsx
+++ b/outputs/candidates/baseline/candidate_04_fatigue.xlsx
@@ -490,7 +490,7 @@
     <t>2203</t>
   </si>
   <si>
-    <t>2165</t>
+    <t>2161</t>
   </si>
   <si>
     <t>353</t>
@@ -520,7 +520,7 @@
     <t>7012</t>
   </si>
   <si>
-    <t>2161</t>
+    <t>2166</t>
   </si>
   <si>
     <t>7020</t>
@@ -3072,7 +3072,7 @@
         <v>85</v>
       </c>
       <c r="Y23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
@@ -4202,7 +4202,7 @@
         <v>2465</v>
       </c>
       <c r="Q2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R2">
         <v>0</v>
